--- a/report-2026-06-02.xlsx
+++ b/report-2026-06-02.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>#</t>
   </si>
@@ -54,10 +54,34 @@
     <t>Error</t>
   </si>
   <si>
+    <t>2026-06-02T21:57:45.080721+05:30</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>21:57:45.080</t>
+  </si>
+  <si>
+    <t>renewed</t>
+  </si>
+  <si>
+    <t>github</t>
+  </si>
+  <si>
+    <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+  </si>
+  <si>
+    <t>PuneetU-EB6LMJD</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-02T21:56:25+05:30</t>
+    <t>2026-06-02T21:57:46+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -589,72 +613,179 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>server+agent</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0h 0m 15s</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-06-02 21:57:30</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Jun 2 07:00 PM</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-06-02 21:57:30</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1h 24m 10s</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>21:57:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>192.168.0.129</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>103.117.15.39</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>windows</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>amd64</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10.0.28</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>agent</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>local</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0h 0m 10s</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-06-02 21:56:15</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Jun 2 07:00 PM</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-06-02 21:56:15</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>1h 23m 5s</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>21:56:25</t>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-06-02 21:57:30</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1h 24m 10s</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>21:57:46</t>
         </is>
       </c>
     </row>
@@ -2019,18 +2150,56 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s">
+    <row r="2">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3">
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="4">
         <v>0</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-02.xlsx
+++ b/report-2026-06-02.xlsx
@@ -81,7 +81,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-02T21:57:46+05:30</t>
+    <t>2026-06-02T21:59:45+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -648,7 +648,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 0m 15s</t>
+          <t>0h 2m 14s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1h 24m 10s</t>
+          <t>1h 26m 10s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:57:46</t>
+          <t>21:59:45</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:57:46</t>
+          <t>21:59:45</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-02.xlsx
+++ b/report-2026-06-02.xlsx
@@ -54,13 +54,13 @@
     <t>Error</t>
   </si>
   <si>
-    <t>2026-06-02T21:57:45.080721+05:30</t>
+    <t>2026-06-02T22:13:27.8102769+05:30</t>
   </si>
   <si>
     <t>2026-06-02</t>
   </si>
   <si>
-    <t>21:57:45.080</t>
+    <t>22:13:27.810</t>
   </si>
   <si>
     <t>renewed</t>
@@ -81,7 +81,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-02T21:59:45+05:30</t>
+    <t>2026-06-02T22:15:28+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -648,12 +648,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 14s</t>
+          <t>0h 2m 13s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-02 21:57:30</t>
+          <t>2026-06-02 22:13:14</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-02 21:57:30</t>
+          <t>2026-06-02 22:13:14</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1h 26m 10s</t>
+          <t>1h 33m 5s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:59:45</t>
+          <t>22:15:28</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-02 21:57:30</t>
+          <t>2026-06-02 22:13:14</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1h 24m 10s</t>
+          <t>1h 31m 5s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:59:45</t>
+          <t>22:15:28</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-02.xlsx
+++ b/report-2026-06-02.xlsx
@@ -16,7 +16,88 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+  <si>
+    <t>PunMonitor Leader Election — Current State</t>
+  </si>
+  <si>
+    <t>Generated 2026-06-02T22:36:03+05:30</t>
+  </si>
+  <si>
+    <t>Election method</t>
+  </si>
+  <si>
+    <t>github</t>
+  </si>
+  <si>
+    <t>GitHub configured</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>GitHub repo</t>
+  </si>
+  <si>
+    <t>puniteswra-spec/PU</t>
+  </si>
+  <si>
+    <t>Self AgentID</t>
+  </si>
+  <si>
+    <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+  </si>
+  <si>
+    <t>Self hostname</t>
+  </si>
+  <si>
+    <t>PuneetU-EB6LMJD</t>
+  </si>
+  <si>
+    <t>Mode / Role</t>
+  </si>
+  <si>
+    <t>SERVER+LEADER (this instance is the GitHub primary)</t>
+  </si>
+  <si>
+    <t>Self is leader</t>
+  </si>
+  <si>
+    <t>YES — this instance is the primary server</t>
+  </si>
+  <si>
+    <t>Current leader</t>
+  </si>
+  <si>
+    <t>Leader last update</t>
+  </si>
+  <si>
+    <t>2026-06-02T22:34:20+05:30 (1m42s ago)</t>
+  </si>
+  <si>
+    <t>Leader stale?</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Last check</t>
+  </si>
+  <si>
+    <t>Check count</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Last error</t>
+  </si>
+  <si>
+    <t>(none)</t>
+  </si>
+  <si>
+    <t>Election History (row-wise — latest first)</t>
+  </si>
   <si>
     <t>#</t>
   </si>
@@ -54,34 +135,25 @@
     <t>Error</t>
   </si>
   <si>
-    <t>2026-06-02T22:13:27.8102769+05:30</t>
+    <t>2026-06-02T22:34:20.8142788+05:30</t>
   </si>
   <si>
     <t>2026-06-02</t>
   </si>
   <si>
-    <t>22:13:27.810</t>
+    <t>22:34:20.814</t>
   </si>
   <si>
     <t>renewed</t>
   </si>
   <si>
-    <t>github</t>
-  </si>
-  <si>
-    <t>PuneetU-EB6LMJD-cf4a9ce5</t>
-  </si>
-  <si>
-    <t>PuneetU-EB6LMJD</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-02T22:15:28+05:30</t>
+    <t>2026-06-02T22:36:03+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -91,7 +163,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,8 +192,20 @@
       <color rgb="FF006100"/>
       <sz val="10"/>
     </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -141,6 +225,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -184,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
@@ -196,6 +290,12 @@
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -608,7 +708,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.28</t>
+          <t>10.0.29</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,12 +748,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 13s</t>
+          <t>0h 1m 56s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-02 22:13:14</t>
+          <t>2026-06-02 22:34:06</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,12 +763,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-02 22:13:14</t>
+          <t>2026-06-02 22:34:06</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1h 33m 5s</t>
+          <t>1h 52m 55s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -678,7 +778,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:15:28</t>
+          <t>22:36:03</t>
         </is>
       </c>
     </row>
@@ -715,7 +815,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.28</t>
+          <t>10.0.29</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -770,12 +870,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-02 22:13:14</t>
+          <t>2026-06-02 22:34:06</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1h 31m 5s</t>
+          <t>1h 51m 10s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -785,7 +885,219 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:15:28</t>
+          <t>22:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>── LATEST GITHUB ELECTION EVENT ──</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[renewed]</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-02T22:34:20.8142788+05:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>22:34:20.814</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>renewed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+        </is>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>renewed</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
@@ -2113,92 +2425,220 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4">
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="4">
+      <c r="B18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="4">
         <v>0</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4">
+      <c r="K18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20">
         <v>1</v>
       </c>
     </row>

--- a/report-2026-06-02.xlsx
+++ b/report-2026-06-02.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-02T22:36:03+05:30</t>
+    <t>Generated 2026-06-02T22:36:20+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-02T22:34:20+05:30 (1m42s ago)</t>
+    <t>2026-06-02T22:34:20+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -153,7 +153,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-02T22:36:03+05:30</t>
+    <t>2026-06-02T22:36:20+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -748,7 +748,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 1m 56s</t>
+          <t>0h 2m 14s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1h 52m 55s</t>
+          <t>1h 53m 10s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:36:03</t>
+          <t>22:36:20</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:36:03</t>
+          <t>22:36:20</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-02.xlsx
+++ b/report-2026-06-02.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-02T22:36:20+05:30</t>
+    <t>Generated 2026-06-02T23:18:21+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -57,43 +57,46 @@
     <t>Mode / Role</t>
   </si>
   <si>
-    <t>SERVER+LEADER (this instance is the GitHub primary)</t>
+    <t>SERVER (primary)</t>
   </si>
   <si>
     <t>Self is leader</t>
   </si>
   <si>
-    <t>YES — this instance is the primary server</t>
+    <t>No</t>
   </si>
   <si>
     <t>Current leader</t>
   </si>
   <si>
+    <t>(no leader recorded)</t>
+  </si>
+  <si>
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-02T22:34:20+05:30 (2m0s ago)</t>
+    <t>(never)</t>
   </si>
   <si>
     <t>Leader stale?</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Last check</t>
   </si>
   <si>
+    <t>2026-06-02T23:16:19+05:30 (2m1s ago)</t>
+  </si>
+  <si>
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>22</t>
   </si>
   <si>
     <t>Last error</t>
   </si>
   <si>
-    <t>(none)</t>
+    <t>auth failed: GitHub API 401 — token revoked or missing scopes</t>
   </si>
   <si>
     <t>Election History (row-wise — latest first)</t>
@@ -135,25 +138,157 @@
     <t>Error</t>
   </si>
   <si>
-    <t>2026-06-02T22:34:20.8142788+05:30</t>
+    <t>2026-06-02T22:54:46.4555913+05:30</t>
   </si>
   <si>
     <t>2026-06-02</t>
   </si>
   <si>
-    <t>22:34:20.814</t>
-  </si>
-  <si>
-    <t>renewed</t>
+    <t>22:54:46.455</t>
+  </si>
+  <si>
+    <t>error</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>auth failed: GitHub API Unauthorized</t>
+  </si>
+  <si>
+    <t>2026-06-02T22:54:52.4559961+05:30</t>
+  </si>
+  <si>
+    <t>22:54:52.455</t>
+  </si>
+  <si>
+    <t>2026-06-02T22:54:57.4565477+05:30</t>
+  </si>
+  <si>
+    <t>22:54:57.456</t>
+  </si>
+  <si>
+    <t>2026-06-02T22:59:59.5186408+05:30</t>
+  </si>
+  <si>
+    <t>22:59:59.518</t>
+  </si>
+  <si>
+    <t>auth failed: Bad credentials — token revoked or missing 'repo' scope. Generate a new token at https://github.com/settings/tokens</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:00:10.2277101+05:30</t>
+  </si>
+  <si>
+    <t>23:00:10.227</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:00:13.2279899+05:30</t>
+  </si>
+  <si>
+    <t>23:00:13.227</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:00:19.2282493+05:30</t>
+  </si>
+  <si>
+    <t>23:00:19.228</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:05:14.5567715+05:30</t>
+  </si>
+  <si>
+    <t>23:05:14.556</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:05:21.5571307+05:30</t>
+  </si>
+  <si>
+    <t>23:05:21.557</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:05:24.5574869+05:30</t>
+  </si>
+  <si>
+    <t>23:05:24.557</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:10:16.5523835+05:30</t>
+  </si>
+  <si>
+    <t>23:10:16.552</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:10:19.5526246+05:30</t>
+  </si>
+  <si>
+    <t>23:10:19.552</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:10:24.5527417+05:30</t>
+  </si>
+  <si>
+    <t>23:10:24.552</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:10:38.1797926+05:30</t>
+  </si>
+  <si>
+    <t>23:10:38.179</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:10:41.1802597+05:30</t>
+  </si>
+  <si>
+    <t>23:10:41.180</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:10:48.1805193+05:30</t>
+  </si>
+  <si>
+    <t>23:10:48.180</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:15:19.7938317+05:30</t>
+  </si>
+  <si>
+    <t>23:15:19.793</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:15:27.0088541+05:30</t>
+  </si>
+  <si>
+    <t>23:15:27.008</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:15:31.0091117+05:30</t>
+  </si>
+  <si>
+    <t>23:15:31.009</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:16:07.5920063+05:30</t>
+  </si>
+  <si>
+    <t>23:16:07.592</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:16:12.5923119+05:30</t>
+  </si>
+  <si>
+    <t>23:16:12.592</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:16:19.5971993+05:30</t>
+  </si>
+  <si>
+    <t>23:16:19.597</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-02T22:36:20+05:30</t>
+    <t>2026-06-02T23:18:21+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -708,7 +843,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.29</t>
+          <t>10.0.30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -748,12 +883,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 14s</t>
+          <t>0h 23m 43s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-02 22:34:06</t>
+          <t>2026-06-02 22:54:37</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -763,12 +898,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-02 22:34:06</t>
+          <t>2026-06-02 22:54:37</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1h 53m 10s</t>
+          <t>2h 29m 25s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -778,7 +913,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:36:20</t>
+          <t>23:18:21</t>
         </is>
       </c>
     </row>
@@ -815,7 +950,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.29</t>
+          <t>10.0.30</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -855,7 +990,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -870,12 +1005,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-02 22:34:06</t>
+          <t>2026-06-02 22:54:37</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1h 51m 10s</t>
+          <t>2h 29m 20s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -885,7 +1020,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:36:20</t>
+          <t>23:18:21</t>
         </is>
       </c>
     </row>
@@ -999,12 +1134,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[renewed]</t>
+          <t>[error]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-02T22:34:20.8142788+05:30</t>
+          <t>2026-06-02T23:16:19.5971993+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1014,12 +1149,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:34:20.814</t>
+          <t>23:16:19.597</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>renewed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1039,20 +1174,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+          <t/>
         </is>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>9223372036</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>renewed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t/>
+          <t>auth failed: GitHub API 401 — token revoked or missing scopes</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2493,23 +2628,23 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -2517,28 +2652,28 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -2554,92 +2689,890 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>1</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="E18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>2</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J18" s="4">
-        <v>0</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>43</v>
+      <c r="H19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s">
+      <c r="A20" s="3">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B20" t="s">
+      <c r="J20" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>5</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>6</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>7</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>9</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>10</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J27" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>11</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J28" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>12</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J29" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J30" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>14</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>15</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>16</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>17</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>18</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>19</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J36" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>20</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J37" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>21</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>22</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J39" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" t="s">
+        <v>91</v>
+      </c>
+      <c r="E41">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-02.xlsx
+++ b/report-2026-06-02.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-02T23:18:21+05:30</t>
+    <t>Generated 2026-06-02T23:28:00+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -84,13 +84,13 @@
     <t>Last check</t>
   </si>
   <si>
-    <t>2026-06-02T23:16:19+05:30 (2m1s ago)</t>
+    <t>2026-06-02T23:27:15+05:30 (44s ago)</t>
   </si>
   <si>
     <t>Check count</t>
   </si>
   <si>
-    <t>22</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -138,13 +138,13 @@
     <t>Error</t>
   </si>
   <si>
-    <t>2026-06-02T22:54:46.4555913+05:30</t>
+    <t>2026-06-02T23:27:02.4756713+05:30</t>
   </si>
   <si>
     <t>2026-06-02</t>
   </si>
   <si>
-    <t>22:54:46.455</t>
+    <t>23:27:02.475</t>
   </si>
   <si>
     <t>error</t>
@@ -156,139 +156,22 @@
     <t>auth failed: GitHub API Unauthorized</t>
   </si>
   <si>
-    <t>2026-06-02T22:54:52.4559961+05:30</t>
-  </si>
-  <si>
-    <t>22:54:52.455</t>
-  </si>
-  <si>
-    <t>2026-06-02T22:54:57.4565477+05:30</t>
-  </si>
-  <si>
-    <t>22:54:57.456</t>
-  </si>
-  <si>
-    <t>2026-06-02T22:59:59.5186408+05:30</t>
-  </si>
-  <si>
-    <t>22:59:59.518</t>
-  </si>
-  <si>
-    <t>auth failed: Bad credentials — token revoked or missing 'repo' scope. Generate a new token at https://github.com/settings/tokens</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:00:10.2277101+05:30</t>
-  </si>
-  <si>
-    <t>23:00:10.227</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:00:13.2279899+05:30</t>
-  </si>
-  <si>
-    <t>23:00:13.227</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:00:19.2282493+05:30</t>
-  </si>
-  <si>
-    <t>23:00:19.228</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:05:14.5567715+05:30</t>
-  </si>
-  <si>
-    <t>23:05:14.556</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:05:21.5571307+05:30</t>
-  </si>
-  <si>
-    <t>23:05:21.557</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:05:24.5574869+05:30</t>
-  </si>
-  <si>
-    <t>23:05:24.557</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:10:16.5523835+05:30</t>
-  </si>
-  <si>
-    <t>23:10:16.552</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:10:19.5526246+05:30</t>
-  </si>
-  <si>
-    <t>23:10:19.552</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:10:24.5527417+05:30</t>
-  </si>
-  <si>
-    <t>23:10:24.552</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:10:38.1797926+05:30</t>
-  </si>
-  <si>
-    <t>23:10:38.179</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:10:41.1802597+05:30</t>
-  </si>
-  <si>
-    <t>23:10:41.180</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:10:48.1805193+05:30</t>
-  </si>
-  <si>
-    <t>23:10:48.180</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:15:19.7938317+05:30</t>
-  </si>
-  <si>
-    <t>23:15:19.793</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:15:27.0088541+05:30</t>
-  </si>
-  <si>
-    <t>23:15:27.008</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:15:31.0091117+05:30</t>
-  </si>
-  <si>
-    <t>23:15:31.009</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:16:07.5920063+05:30</t>
-  </si>
-  <si>
-    <t>23:16:07.592</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:16:12.5923119+05:30</t>
-  </si>
-  <si>
-    <t>23:16:12.592</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:16:19.5971993+05:30</t>
-  </si>
-  <si>
-    <t>23:16:19.597</t>
+    <t>2026-06-02T23:27:08.476131+05:30</t>
+  </si>
+  <si>
+    <t>23:27:08.476</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:27:15.4767145+05:30</t>
+  </si>
+  <si>
+    <t>23:27:15.476</t>
   </si>
   <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-02T23:18:21+05:30</t>
+    <t>2026-06-02T23:28:00+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -843,7 +726,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.30</t>
+          <t>10.0.31</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -883,12 +766,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 23m 43s</t>
+          <t>0h 1m 7s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-02 22:54:37</t>
+          <t>2026-06-02 23:26:52</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -898,12 +781,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-02 22:54:37</t>
+          <t>2026-06-02 23:26:52</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2h 29m 25s</t>
+          <t>2h 36m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -913,7 +796,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>23:18:21</t>
+          <t>23:28:00</t>
         </is>
       </c>
     </row>
@@ -950,7 +833,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.30</t>
+          <t>10.0.31</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -990,7 +873,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1005,12 +888,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-02 22:54:37</t>
+          <t>2026-06-02 23:26:52</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2h 29m 20s</t>
+          <t>2h 35m 50s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1020,7 +903,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>23:18:21</t>
+          <t>23:28:00</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1022,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-02T23:16:19.5971993+05:30</t>
+          <t>2026-06-02T23:27:15.4767145+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1149,7 +1032,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23:16:19.597</t>
+          <t>23:27:15.476</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2839,740 +2722,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3">
-        <v>4</v>
-      </c>
-      <c r="B21" s="3" t="s">
+    <row r="22">
+      <c r="A22" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="B22" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22">
         <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J21" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3">
-        <v>5</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J22" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3">
-        <v>6</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J23" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3">
-        <v>7</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J24" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3">
-        <v>8</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J25" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3">
-        <v>9</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J26" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3">
-        <v>10</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J27" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3">
-        <v>11</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J28" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3">
-        <v>12</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J29" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3">
-        <v>13</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J30" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3">
-        <v>14</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J31" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3">
-        <v>15</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J32" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3">
-        <v>16</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J33" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3">
-        <v>17</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J34" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3">
-        <v>18</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J35" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3">
-        <v>19</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J36" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3">
-        <v>20</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J37" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3">
-        <v>21</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J38" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3">
-        <v>22</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J39" s="3">
-        <v>9223372036</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>89</v>
-      </c>
-      <c r="B41" t="s">
-        <v>90</v>
-      </c>
-      <c r="D41" t="s">
-        <v>91</v>
-      </c>
-      <c r="E41">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-02.xlsx
+++ b/report-2026-06-02.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-02T23:28:00+05:30</t>
+    <t>Generated 2026-06-02T23:29:18+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -84,7 +84,7 @@
     <t>Last check</t>
   </si>
   <si>
-    <t>2026-06-02T23:27:15+05:30 (44s ago)</t>
+    <t>2026-06-02T23:27:15+05:30 (2m2s ago)</t>
   </si>
   <si>
     <t>Check count</t>
@@ -171,7 +171,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-02T23:28:00+05:30</t>
+    <t>2026-06-02T23:29:18+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -766,7 +766,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 1m 7s</t>
+          <t>0h 2m 25s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2h 36m 15s</t>
+          <t>2h 37m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>23:28:00</t>
+          <t>23:29:18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>23:28:00</t>
+          <t>23:29:18</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-02.xlsx
+++ b/report-2026-06-02.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-02T23:29:18+05:30</t>
+    <t>Generated 2026-06-02T23:34:39+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -84,13 +84,13 @@
     <t>Last check</t>
   </si>
   <si>
-    <t>2026-06-02T23:27:15+05:30 (2m2s ago)</t>
+    <t>2026-06-02T23:32:38+05:30 (2m1s ago)</t>
   </si>
   <si>
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>7</t>
   </si>
   <si>
     <t>Last error</t>
@@ -168,10 +168,37 @@
     <t>23:27:15.476</t>
   </si>
   <si>
+    <t>2026-06-02T23:32:19.6548022+05:30</t>
+  </si>
+  <si>
+    <t>23:32:19.654</t>
+  </si>
+  <si>
+    <t>renewed</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:32:29.136574+05:30</t>
+  </si>
+  <si>
+    <t>23:32:29.136</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:32:35.136756+05:30</t>
+  </si>
+  <si>
+    <t>23:32:35.136</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:32:38.1370128+05:30</t>
+  </si>
+  <si>
+    <t>23:32:38.137</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-02T23:29:18+05:30</t>
+    <t>2026-06-02T23:34:39+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -766,7 +793,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 25s</t>
+          <t>0h 7m 47s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -786,7 +813,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2h 37m 35s</t>
+          <t>2h 40m 45s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -796,7 +823,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>23:29:18</t>
+          <t>23:34:39</t>
         </is>
       </c>
     </row>
@@ -873,7 +900,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>347</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -893,7 +920,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2h 35m 50s</t>
+          <t>2h 39m 40s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -903,7 +930,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>23:29:18</t>
+          <t>23:34:39</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1049,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-02T23:27:15.4767145+05:30</t>
+          <t>2026-06-02T23:32:38.1370128+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1032,7 +1059,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23:27:15.476</t>
+          <t>23:32:38.137</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2722,18 +2749,170 @@
         <v>26</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="4">
+        <v>4</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22">
+      <c r="A22" s="3">
+        <v>5</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>6</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>7</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-02.xlsx
+++ b/report-2026-06-02.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-02T23:34:39+05:30</t>
+    <t>Generated 2026-06-02T23:59:57+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -57,148 +57,212 @@
     <t>Mode / Role</t>
   </si>
   <si>
-    <t>SERVER (primary)</t>
+    <t>SERVER+LEADER (this instance is the GitHub primary)</t>
   </si>
   <si>
     <t>Self is leader</t>
   </si>
   <si>
+    <t>YES — this instance is the primary server</t>
+  </si>
+  <si>
+    <t>Current leader</t>
+  </si>
+  <si>
+    <t>Leader last update</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:57:57+05:30 (2m0s ago)</t>
+  </si>
+  <si>
+    <t>Leader stale?</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Current leader</t>
-  </si>
-  <si>
-    <t>(no leader recorded)</t>
-  </si>
-  <si>
-    <t>Leader last update</t>
-  </si>
-  <si>
-    <t>(never)</t>
-  </si>
-  <si>
-    <t>Leader stale?</t>
-  </si>
-  <si>
     <t>Last check</t>
   </si>
   <si>
-    <t>2026-06-02T23:32:38+05:30 (2m1s ago)</t>
-  </si>
-  <si>
     <t>Check count</t>
   </si>
   <si>
-    <t>7</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
   </si>
   <si>
+    <t>(none)</t>
+  </si>
+  <si>
+    <t>Election History (row-wise — latest first)</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Agent ID (self)</t>
+  </si>
+  <si>
+    <t>Hostname</t>
+  </si>
+  <si>
+    <t>Leader ID</t>
+  </si>
+  <si>
+    <t>Leader Age (sec)</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:42:23.1496213+05:30</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>23:42:23.149</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>auth failed: GitHub API Unauthorized</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:42:28.149829+05:30</t>
+  </si>
+  <si>
+    <t>23:42:28.149</t>
+  </si>
+  <si>
     <t>auth failed: GitHub API 401 — token revoked or missing scopes</t>
   </si>
   <si>
-    <t>Election History (row-wise — latest first)</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Agent ID (self)</t>
-  </si>
-  <si>
-    <t>Hostname</t>
-  </si>
-  <si>
-    <t>Leader ID</t>
-  </si>
-  <si>
-    <t>Leader Age (sec)</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Error</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:27:02.4756713+05:30</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
-    <t>23:27:02.475</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>auth failed: GitHub API Unauthorized</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:27:08.476131+05:30</t>
-  </si>
-  <si>
-    <t>23:27:08.476</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:27:15.4767145+05:30</t>
-  </si>
-  <si>
-    <t>23:27:15.476</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:32:19.6548022+05:30</t>
-  </si>
-  <si>
-    <t>23:32:19.654</t>
+    <t>2026-06-02T23:42:31.1501348+05:30</t>
+  </si>
+  <si>
+    <t>23:42:31.150</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:45:06.7698696+05:30</t>
+  </si>
+  <si>
+    <t>23:45:06.769</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:45:11.7706387+05:30</t>
+  </si>
+  <si>
+    <t>23:45:11.770</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:45:15.7709227+05:30</t>
+  </si>
+  <si>
+    <t>23:45:15.770</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:50:17.8165284+05:30</t>
+  </si>
+  <si>
+    <t>23:50:17.816</t>
+  </si>
+  <si>
+    <t>auth failed: Bad credentials (token type: unknown).
+Generate a new Classic token with 'repo' scope at https://github.com/settings/tokens</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:50:36.5502294+05:30</t>
+  </si>
+  <si>
+    <t>23:50:36.550</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:50:43.5510827+05:30</t>
+  </si>
+  <si>
+    <t>23:50:43.551</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:50:46.5520713+05:30</t>
+  </si>
+  <si>
+    <t>23:50:46.552</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:52:41.401389+05:30</t>
+  </si>
+  <si>
+    <t>23:52:41.401</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:52:48.401713+05:30</t>
+  </si>
+  <si>
+    <t>23:52:48.401</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:52:54.4018629+05:30</t>
+  </si>
+  <si>
+    <t>23:52:54.401</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:53:29.7147888+05:30</t>
+  </si>
+  <si>
+    <t>23:53:29.714</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:53:33.7149024+05:30</t>
+  </si>
+  <si>
+    <t>23:53:33.714</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:53:36.7150546+05:30</t>
+  </si>
+  <si>
+    <t>23:53:36.715</t>
+  </si>
+  <si>
+    <t>2026-06-02T23:57:19.9492727+05:30</t>
+  </si>
+  <si>
+    <t>23:57:19.949</t>
   </si>
   <si>
     <t>renewed</t>
   </si>
   <si>
-    <t>2026-06-02T23:32:29.136574+05:30</t>
-  </si>
-  <si>
-    <t>23:32:29.136</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:32:35.136756+05:30</t>
-  </si>
-  <si>
-    <t>23:32:35.136</t>
-  </si>
-  <si>
-    <t>2026-06-02T23:32:38.1370128+05:30</t>
-  </si>
-  <si>
-    <t>23:32:38.137</t>
-  </si>
-  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-02T23:34:39+05:30</t>
+    <t>2026-06-02T23:59:57+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -753,7 +817,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.31</t>
+          <t>10.0.33</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -793,12 +857,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 47s</t>
+          <t>0h 2m 13s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-02 23:26:52</t>
+          <t>2026-06-02 23:57:44</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -808,12 +872,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-02 23:26:52</t>
+          <t>2026-06-02 23:57:44</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2h 40m 45s</t>
+          <t>3h 1m 55s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -823,7 +887,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>23:34:39</t>
+          <t>23:59:57</t>
         </is>
       </c>
     </row>
@@ -860,7 +924,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.31</t>
+          <t>10.0.33</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -900,7 +964,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -915,12 +979,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-02 23:26:52</t>
+          <t>2026-06-02 23:57:44</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2h 39m 40s</t>
+          <t>2h 59m 55s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -930,7 +994,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>23:34:39</t>
+          <t>23:59:57</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1108,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[error]</t>
+          <t>[renewed]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-02T23:32:38.1370128+05:30</t>
+          <t>2026-06-02T23:57:19.9492727+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1059,12 +1123,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23:32:38.137</t>
+          <t>23:57:19.949</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>renewed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1084,20 +1148,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t/>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
       <c r="J5">
-        <v>9223372036</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>renewed</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>auth failed: GitHub API 401 — token revoked or missing scopes</t>
+          <t/>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2538,23 +2602,23 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -2562,28 +2626,28 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -2599,40 +2663,40 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -2640,16 +2704,16 @@
         <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -2661,16 +2725,16 @@
         <v>11</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J18" s="3">
         <v>9223372036</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -2678,16 +2742,16 @@
         <v>2</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>3</v>
@@ -2699,16 +2763,16 @@
         <v>11</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J19" s="3">
         <v>9223372036</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
@@ -2719,13 +2783,13 @@
         <v>48</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -2737,53 +2801,53 @@
         <v>11</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J20" s="3">
         <v>9223372036</v>
       </c>
       <c r="K20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4">
-        <v>4</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="4">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="L21" s="4" t="s">
+      <c r="J21" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2792,16 +2856,16 @@
         <v>5</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -2813,16 +2877,16 @@
         <v>11</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J22" s="3">
         <v>9223372036</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -2830,16 +2894,16 @@
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>3</v>
@@ -2851,16 +2915,16 @@
         <v>11</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J23" s="3">
         <v>9223372036</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
@@ -2868,16 +2932,16 @@
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -2889,30 +2953,410 @@
         <v>11</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J24" s="3">
         <v>9223372036</v>
       </c>
       <c r="K24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>26</v>
+      <c r="J25" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="A26" s="3">
+        <v>9</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E26">
-        <v>7</v>
+      <c r="C26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J26" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>10</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>11</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J28" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>12</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J29" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J30" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>14</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J31" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>15</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J32" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>16</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J33" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4">
+        <v>17</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" s="4">
+        <v>0</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
